--- a/client-docs/test-cases/emg-o-test-cases-e2e-mode2.xlsx
+++ b/client-docs/test-cases/emg-o-test-cases-e2e-mode2.xlsx
@@ -669,8 +669,8 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>ลูกค้า = "E2E Test Customer"
-สินค้า = บลู ซุปเปอร์เจนติ/BLUE SERPERGENTI - Slab, Finish = Polished</t>
+          <t>ลูกค้า = "ทดสอบ E2E - Test Customer"
+สินค้า = E2E Mode2 Serial Fresh - Slab</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>กด "Select Slabs" เลือกแผ่นตามเลข Serial (รองรับเลือกหลายแผ่นพร้อมกันในคลิกเดียว)</t>
+          <t>กด "Select Slabs" เลือกแผ่นตามเลข Serial</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -708,18 +708,18 @@
       <c r="D5" s="7" t="inlineStr">
         <is>
           <t>1. กดปุ่ม "Select Slabs" บนบรรทัด
-2. กด "Add a line" — หน้าต่างเลือกแผ่นแสดงรายการแผ่น Available พร้อมเลข Serial/ขนาด/สถานะ ติ๊กเลือกได้หลายแผ่นพร้อมกัน
-3. กด Select แล้วกด "Confirm Selection"</t>
+2. กด "Add a line" — หน้าต่างเลือกแผ่นแสดงรายการแผ่น Available พร้อมเลข Serial/ขนาด/สถานะ
+3. ติ๊กเลือกแผ่น กด "Select" แล้วกด "Confirm Selection"</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>เลือกแผ่น = BLK-26-0050 #1</t>
+          <t>เลือกแผ่น = BLK-26-0026 #1 (BLK-26-0026-1)</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>บรรทัด SO ผูกแผ่นที่เลือก จำนวน/ราคาต่อหน่วยเติมอัตโนมัติจากขนาด+ราคาจริงของแผ่น</t>
+          <t>บรรทัด SO ผูกแผ่นที่เลือก จำนวน/ราคาต่อหน่วยเติมอัตโนมัติจากขนาด+ราคาจริงของแผ่น (ตัวอย่างจริง: 0.96 ตร.ม. × 4,500/ตร.ม. = 4,320)</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>ช่อง Analytic Distribution ต้องมีค่าติดมาอัตโนมัติแล้วตั้งแต่ก่อน Confirm (Category + Material + Block รวม 3 มิติ) — SO เปลี่ยนสถานะเป็น Sales Order มี Delivery Order เกิดขึ้นอัตโนมัติ 1 ใบ</t>
+          <t>ช่อง Analytic Distribution ต้องมีค่าติดมาอัตโนมัติแล้วตั้งแต่ก่อน Confirm (Material + Block + หมวดวัสดุ รวม 3 มิติ) — SO เปลี่ยนสถานะเป็น Sales Order มี Delivery Order เกิดขึ้นอัตโนมัติ 1 ใบ (ตัวอย่างจริง: S00123 → EG01/OUT/00077)</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>สินค้า = ดำอัฟริกา/BLACK AFRICA - Slab (Material โหมด Lot)</t>
+          <t>สินค้า = E2E Mode2 Lot Fresh - Slab (Material โหมด Lot)</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -946,13 +946,13 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Lot = BLK-26-0047 (เหลือ 6.00 ตร.ม. เต็มล็อต)
-Quantity to Sell (Sq.Mt.) = 2.00</t>
+          <t>Lot = BLK-26-0027 (เหลือ 1.00 ตร.ม. เต็มล็อต)
+Quantity to Sell (Sq.Mt.) = 0.50</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>บรรทัด SO ผูก Lot ถูกต้อง จำนวน/ราคารวมปรับตาม 2.00 ตร.ม. ที่เลือกทันที (ตัวอย่างจริง: 2.00 × 4,000/ตร.ม. = 8,000) ไม่มีการเลือกแผ่นเดี่ยวใดๆ</t>
+          <t>บรรทัด SO ผูก Lot ถูกต้อง จำนวน/ราคารวมปรับตาม 0.50 ตร.ม. ที่เลือกทันที (ตัวอย่างจริง: 0.50 × 4,000/ตร.ม. = 2,000) ไม่มีการเลือกแผ่นเดี่ยวใดๆ</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -960,7 +960,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H5" s="7" t="n"/>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>✅ พบ+แก้บั๊กจริงระหว่างสร้างเคสนี้ (2026-09-14): กลไกตัดหินใหม่ (แทนที่ Factory Worklist เดิม เมื่อวาน) ไม่ได้ผูก lot ก้อนที่ตัดเข้ากับ material_lot_id ของ bundle ทำให้ขายผ่านปุ่มนี้ไม่ได้เลย (ระบบเห็นสต็อกเหลือ 0 ทั้งที่มีจริง) แก้ไขที่โค้ด (mrp_production.py เรียกใช้ _ensure_material_lot() ที่มีอยู่แล้ว) deploy แล้วบน mbx-ee-dev ตัวเลขด้านล่างมาจากการรันซ้ำหลังแก้แล้วจริง</t>
+        </is>
+      </c>
       <c r="I5" s="7" t="n"/>
       <c r="J5" s="7" t="n"/>
       <c r="K5" s="7" t="n"/>
@@ -995,7 +999,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>ช่อง Analytic Distribution มีค่าติดมาอัตโนมัติเหมือนโหมด Serial — SO เปลี่ยนสถานะเป็น Sales Order มี Delivery Order เกิดขึ้นอัตโนมัติ 1 ใบ — ตัวอย่างจริง: S00111 ส่วนที่เหลือของล็อตเดิม (4.00 ตร.ม.) ยังคงพร้อมขายต่อได้ตามปกติ</t>
+          <t>ช่อง Analytic Distribution มีค่าติดมาอัตโนมัติเหมือนโหมด Serial — SO เปลี่ยนสถานะเป็น Sales Order มี Delivery Order เกิดขึ้นอัตโนมัติ 1 ใบ — ตัวอย่างจริง: S00124 → EG01/OUT/00078 ส่วนที่เหลือของล็อตเดิม (0.50 ตร.ม.) ยังคงพร้อมขายต่อได้ตามปกติ</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -1148,7 +1152,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>หมายเหตุ: กันส่งแผ่น/ล็อตผิดให้ลูกค้าโดยไม่ได้ตรวจสอบก่อน (ADR-009) — ใช้ตรรกะเดียวกันไม่ว่าเป็นบรรทัด Serial หรือ Lot ยืนยันแล้วทั้งคู่จริงในรอบนี้ (ไม่ใช่แค่ Serial แบบ v1)</t>
+          <t>หมายเหตุ: กันส่งแผ่น/ล็อตผิดให้ลูกค้าโดยไม่ได้ตรวจสอบก่อน (ADR-009) — ใช้ตรรกะเดียวกันไม่ว่าเป็นบรรทัด Serial หรือ Lot ยืนยันแล้วทั้งคู่จริงในรอบนี้</t>
         </is>
       </c>
       <c r="I4" s="7" t="n"/>
@@ -1181,8 +1185,8 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Scanned Serial (Serial path) = BLK-26-0050-1
-Scanned Serial (Lot path) = BLK-26-0047-LOT</t>
+          <t>Scanned Serial (Serial path) = BLK-26-0026-1
+Scanned Serial (Lot path) = BLK-26-0027-LOT</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -1320,7 +1324,7 @@
       <c r="D4" s="7" t="inlineStr">
         <is>
           <t>1. เปิด Sale Order &gt; กด "Create Invoice"
-2. เลือก "Regular invoice" &gt; Create Draft Invoice
+2. เลือก "Regular invoice" &gt; Create Draft
 3. เปิดใบแจ้งหนี้ &gt; กด Confirm</t>
         </is>
       </c>
@@ -1331,7 +1335,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>ใบแจ้งหนี้สถานะ Posted ยอดรวมตรงกับ SO รวม VAT — ตัวอย่างจริง Lot: INV/2026/00009 (8,560.00)</t>
+          <t>ใบแจ้งหนี้สถานะ Posted ยอดรวมตรงกับ SO รวม VAT — ตัวอย่างจริง Lot: INV/2026/00026 (2,140.00)</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -1374,7 +1378,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>ใบแจ้งหนี้ขึ้นสถานะ "Paid" (Payment Status) — ตัวอย่างจริงทั้งคู่ (INV/2026/00008, INV/2026/00009) จบที่สถานะ Posted + Paid</t>
+          <t>ใบแจ้งหนี้ขึ้นสถานะ "In Payment" — ตัวอย่างจริงทั้งคู่ (INV/2026/00025, INV/2026/00026) จบที่สถานะ Posted + In Payment</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -1416,7 +1420,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>บรรทัดรายได้ต้องขึ้นบัญชีถูกโหมด — Serial = "Sales Revenue - Serial Slab Sale (Mode 2)", Lot = "Sales Revenue - Lot Material (Mode 2)" — พร้อม Analytic Distribution ครบ ตรงกับใน SO</t>
+          <t>บรรทัดรายได้ต้องขึ้นบัญชีถูกโหมด — Serial = "411160 Sales Revenue - Serial Slab Sale (Mode 2)", Lot = "411120 Sales Revenue - Lot Material (Mode 2)" — พร้อม Analytic Distribution ครบ ตรงกับใน SO</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -1424,11 +1428,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>✅ แก้บั๊กจริงแล้ว (2026-09-09): ก่อนหน้านี้ Serial-mode ทุกเคสลงบัญชีรายได้ผิดเป็นของ Mode 3 (Cut-to-Order) — เจอจากการทดสอบนี้เอง แก้ไขที่โค้ด (สร้างบัญชีใหม่ "Sales Revenue - Serial Slab Sale (Mode 2)") และ verify แล้วว่าเคสใหม่ๆ ขึ้นบัญชีถูกต้องเองอัตโนมัติ ไม่ต้องแก้มือ</t>
-        </is>
-      </c>
+      <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="n"/>
       <c r="J6" s="7" t="n"/>
       <c r="K6" s="7" t="n"/>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>ทำ TC-E2E-M2-08 เสร็จแล้ว (Delivery = Done), ใช้ Invoice ฝั่ง Serial (INV/2026/00008)</t>
+          <t>ทำ TC-E2E-M2-08 เสร็จแล้ว (Delivery = Done), ใช้ Invoice ฝั่ง Serial (INV/2026/00025)</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>เห็นคู่ COGS/Inventory แนบอัตโนมัติบนใบแจ้งหนี้ใบเดียวกัน (เดบิต "COGS - Stone Sales (all modes)" / เครดิต "Inventory - Stone Blocks (Raw)") พร้อม Analytic Distribution ตรงกับบรรทัดรายได้ — ตัวอย่างจริง INV/2026/00008: 9,000.00 ทั้งคู่ (ราคาขายของ Material ตัวอย่างนี้บังเอิญยังไม่ได้ตั้งไว้เลยโชว์รายได้ 0 — ไม่เกี่ยวกับ COGS ที่กำลังเช็ค)</t>
+          <t>เห็นคู่ COGS/Inventory แนบอัตโนมัติบนใบแจ้งหนี้ใบเดียวกัน (เดบิต "511110 COGS - Stone Sales (all modes)" / เครดิต "113110 Inventory - Stone Blocks (Raw)") พร้อม Analytic Distribution ตรงกับบรรทัดรายได้ — ตัวอย่างจริง INV/2026/00025: COGS/Inventory คู่ละ 300.00 (ยอดรวมสมดุล 4,922.40 = 4,922.40)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -1470,11 +1470,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>✅ แก้บั๊กจริงแล้ว (2026-09-09): ก่อนหน้านี้แทบทุก Bundle ในระบบ (ที่ไม่ได้สร้างผ่าน Session นี้) ไม่เคยมีต้นทุนจริงถูกฝังเข้าไปในระบบ valuation ของ Odoo เลย (ทั้งที่ตัวเลขต้นทุนในโมดูลเองถูกต้องอยู่แล้ว) ทำให้ COGS ออกมาเป็น 0 บาททุกครั้ง — backfill ต้นทุนที่ขาดหายทั้งระดับ Block และระดับ Slab (แยกกันคนละจุด) ทั้ง 2 ฐานข้อมูลแล้ว ยืนยันด้วย live test จริงว่า COGS ขึ้นถูกต้อง</t>
-        </is>
-      </c>
+      <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
       <c r="J7" s="7" t="n"/>
       <c r="K7" s="7" t="n"/>
@@ -1488,12 +1484,12 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>⚠️ ตรวจ Lot-mode COGS — ยังไม่ผ่าน (known issue เปิดอยู่)</t>
+          <t>ตรวจ Lot-mode COGS ลงบัญชีถูกต้องหรือไม่</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>ทำ TC-E2E-M2-08 เสร็จแล้ว (Delivery = Done), ใช้ Invoice ฝั่ง Lot (INV/2026/00009)</t>
+          <t>ทำ TC-E2E-M2-08 เสร็จแล้ว (Delivery = Done), ใช้ Invoice ฝั่ง Lot (INV/2026/00026)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -1509,7 +1505,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>(ยังไม่ผ่าน) ตัวอย่างจริง INV/2026/00009: มีแค่บรรทัดรายได้/VAT/ลูกหนี้ — ไม่มีคู่ COGS/Inventory เลย ทั้งที่ Material นี้ตั้งค่าเป็น real_time/FIFO เหมือนกับฝั่ง Serial</t>
+          <t>เห็นคู่ COGS/Inventory แนบอัตโนมัติเหมือนฝั่ง Serial — ตัวอย่างจริง INV/2026/00026: COGS/Inventory คู่ละ 120.00 (ยอดรวมสมดุล 2,260.00 = 2,260.00) ไม่ใช่ 0 บาทอีกต่อไป</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -1519,7 +1515,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>⚠️ พบบั๊กจริง ยังไม่ได้แก้ (2026-09-09): ต่างจาก Serial-mode ข้างบน โหมด Lot ยังโพสต์ COGS เป็น 0 อยู่ แม้ backfill ต้นทุนแล้ว — ตรวจโค้ดพบว่า FIFO layer ที่รับเข้ามา (มีมูลค่าจริงถูกต้อง) ไม่ถูกดึงมาใช้ตอนส่งของเลย (remaining quantity ไม่ลดลงหลังขายจริง) สาเหตุที่แท้จริงยังไม่พบ ต้องสืบเพิ่มอีก Session หน้า</t>
+          <t>✅ เดิมเป็น known issue เปิดอยู่ (Lot-mode COGS ขึ้น 0 บาทเสมอ, v1/v2) — ตอนนี้ปิดแล้วจริง เป็นผลพลอยได้จากการแก้บั๊ก material_lot_id ในเคส TC-E2E-M2-05 (สาเหตุเดียวกัน: lot ที่ผูกผิดทำให้ FIFO หาต้นทุนที่ถูกต้องไม่เจอ) ยืนยันด้วยการรันจริงรอบนี้ COGS ขึ้นถูกต้องไม่ใช่ 0 อีกต่อไป</t>
         </is>
       </c>
       <c r="I8" s="7" t="n"/>

--- a/client-docs/test-cases/emg-o-test-cases-e2e-mode2.xlsx
+++ b/client-docs/test-cases/emg-o-test-cases-e2e-mode2.xlsx
@@ -670,7 +670,7 @@
       <c r="E4" s="7" t="inlineStr">
         <is>
           <t>ลูกค้า = "ทดสอบ E2E - Test Customer"
-สินค้า = E2E Mode2 Serial Fresh - Slab</t>
+สินค้า = E2E Mode2 Serial Fresh V2 - Slab</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>เลือกแผ่น = BLK-26-0026 #1 (BLK-26-0026-1)</t>
+          <t>เลือกแผ่น = BLK-26-0034 #1 (BLK-26-0034-1)</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>ช่อง Analytic Distribution ต้องมีค่าติดมาอัตโนมัติแล้วตั้งแต่ก่อน Confirm (Material + Block + หมวดวัสดุ รวม 3 มิติ) — SO เปลี่ยนสถานะเป็น Sales Order มี Delivery Order เกิดขึ้นอัตโนมัติ 1 ใบ (ตัวอย่างจริง: S00123 → EG01/OUT/00077)</t>
+          <t>ช่อง Analytic Distribution ต้องมีค่าติดมาอัตโนมัติแล้วตั้งแต่ก่อน Confirm (Material + Block + หมวดวัสดุ รวม 3 มิติ) — SO เปลี่ยนสถานะเป็น Sales Order มี Delivery Order เกิดขึ้นอัตโนมัติ 1 ใบ (ตัวอย่างจริง: S00133 → EG01/OUT/00087)</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>สินค้า = E2E Mode2 Lot Fresh - Slab (Material โหมด Lot)</t>
+          <t>สินค้า = E2E Mode2 Lot Fresh V2 - Slab (Material โหมด Lot)</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -946,13 +946,13 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Lot = BLK-26-0027 (เหลือ 1.00 ตร.ม. เต็มล็อต)
-Quantity to Sell (Sq.Mt.) = 0.50</t>
+          <t>Lot = BLK-26-0035 (เหลือ 5.00 ตร.ม. เต็มล็อต)
+Quantity to Sell (Sq.Mt.) = 2.00</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>บรรทัด SO ผูก Lot ถูกต้อง จำนวน/ราคารวมปรับตาม 0.50 ตร.ม. ที่เลือกทันที (ตัวอย่างจริง: 0.50 × 4,000/ตร.ม. = 2,000) ไม่มีการเลือกแผ่นเดี่ยวใดๆ</t>
+          <t>บรรทัด SO ผูก Lot ถูกต้อง จำนวน/ราคารวมปรับตาม 2.00 ตร.ม. ที่เลือกทันที (ตัวอย่างจริง: 2.00 × 4,000/ตร.ม. = 8,000) ไม่มีการเลือกแผ่นเดี่ยวใดๆ</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>✅ พบ+แก้บั๊กจริงระหว่างสร้างเคสนี้ (2026-09-14): กลไกตัดหินใหม่ (แทนที่ Factory Worklist เดิม เมื่อวาน) ไม่ได้ผูก lot ก้อนที่ตัดเข้ากับ material_lot_id ของ bundle ทำให้ขายผ่านปุ่มนี้ไม่ได้เลย (ระบบเห็นสต็อกเหลือ 0 ทั้งที่มีจริง) แก้ไขที่โค้ด (mrp_production.py เรียกใช้ _ensure_material_lot() ที่มีอยู่แล้ว) deploy แล้วบน mbx-ee-dev ตัวเลขด้านล่างมาจากการรันซ้ำหลังแก้แล้วจริง</t>
+          <t>✅ ยืนยันซ้ำ (2026-09-16): บั๊กเดิม (lot ที่ตัดใหม่ไม่ผูกกับ material_lot_id ของ bundle ทำให้ขายผ่านปุ่มนี้ไม่ได้) ยังคงปิดอยู่จริง — ครั้งนี้ตัดสต๊อกใหม่ 5 แผ่น (5.00 ตร.ม.) ผ่านกลไก MO เดียวกับ Mode 3 แล้วรวมเป็นล็อตเดียวถูกต้องอัตโนมัติทันที ไม่ต้องแก้โค้ดเพิ่ม</t>
         </is>
       </c>
       <c r="I5" s="7" t="n"/>
@@ -999,7 +999,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>ช่อง Analytic Distribution มีค่าติดมาอัตโนมัติเหมือนโหมด Serial — SO เปลี่ยนสถานะเป็น Sales Order มี Delivery Order เกิดขึ้นอัตโนมัติ 1 ใบ — ตัวอย่างจริง: S00124 → EG01/OUT/00078 ส่วนที่เหลือของล็อตเดิม (0.50 ตร.ม.) ยังคงพร้อมขายต่อได้ตามปกติ</t>
+          <t>ช่อง Analytic Distribution มีค่าติดมาอัตโนมัติเหมือนโหมด Serial — SO เปลี่ยนสถานะเป็น Sales Order มี Delivery Order เกิดขึ้นอัตโนมัติ 1 ใบ — ตัวอย่างจริง: S00134 → EG01/OUT/00088 ส่วนที่เหลือของล็อตเดิม (3.00 ตร.ม.) ยังคงพร้อมขายต่อได้ตามปกติ</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -1185,8 +1185,8 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Scanned Serial (Serial path) = BLK-26-0026-1
-Scanned Serial (Lot path) = BLK-26-0027-LOT</t>
+          <t>Scanned Serial (Serial path) = BLK-26-0034-1
+Scanned Serial (Lot path) = BLK-26-0035-LOT</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>ใบแจ้งหนี้สถานะ Posted ยอดรวมตรงกับ SO รวม VAT — ตัวอย่างจริง Lot: INV/2026/00026 (2,140.00)</t>
+          <t>ใบแจ้งหนี้สถานะ Posted ยอดรวมตรงกับ SO รวม VAT — ตัวอย่างจริง Lot: INV/2026/00036 (8,560.00)</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>ใบแจ้งหนี้ขึ้นสถานะ "In Payment" — ตัวอย่างจริงทั้งคู่ (INV/2026/00025, INV/2026/00026) จบที่สถานะ Posted + In Payment</t>
+          <t>ใบแจ้งหนี้ขึ้นสถานะ "In Payment" — ตัวอย่างจริงทั้งคู่ (INV/2026/00035, INV/2026/00036) จบที่สถานะ Posted + In Payment</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>ทำ TC-E2E-M2-08 เสร็จแล้ว (Delivery = Done), ใช้ Invoice ฝั่ง Serial (INV/2026/00025)</t>
+          <t>ทำ TC-E2E-M2-08 เสร็จแล้ว (Delivery = Done), ใช้ Invoice ฝั่ง Serial (INV/2026/00035)</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>เห็นคู่ COGS/Inventory แนบอัตโนมัติบนใบแจ้งหนี้ใบเดียวกัน (เดบิต "511110 COGS - Stone Sales (all modes)" / เครดิต "113110 Inventory - Stone Blocks (Raw)") พร้อม Analytic Distribution ตรงกับบรรทัดรายได้ — ตัวอย่างจริง INV/2026/00025: COGS/Inventory คู่ละ 300.00 (ยอดรวมสมดุล 4,922.40 = 4,922.40)</t>
+          <t>เห็นคู่ COGS/Inventory แนบอัตโนมัติบนใบแจ้งหนี้ใบเดียวกัน (เดบิต "511110 COGS - Stone Sales (all modes)" / เครดิต "113110 Inventory - Stone Blocks (Raw)") พร้อม Analytic Distribution ตรงกับบรรทัดรายได้ — ตัวอย่างจริง INV/2026/00035: COGS/Inventory คู่ละ 200.00 (ยอดรวมสมดุล 4,822.40 = 4,822.40)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>ทำ TC-E2E-M2-08 เสร็จแล้ว (Delivery = Done), ใช้ Invoice ฝั่ง Lot (INV/2026/00026)</t>
+          <t>ทำ TC-E2E-M2-08 เสร็จแล้ว (Delivery = Done), ใช้ Invoice ฝั่ง Lot (INV/2026/00036)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>เห็นคู่ COGS/Inventory แนบอัตโนมัติเหมือนฝั่ง Serial — ตัวอย่างจริง INV/2026/00026: COGS/Inventory คู่ละ 120.00 (ยอดรวมสมดุล 2,260.00 = 2,260.00) ไม่ใช่ 0 บาทอีกต่อไป</t>
+          <t>เห็นคู่ COGS/Inventory แนบอัตโนมัติเหมือนฝั่ง Serial — ตัวอย่างจริง INV/2026/00036: COGS/Inventory คู่ละ 320.00 (ยอดรวมสมดุล 8,880.00 = 8,880.00) ไม่ใช่ 0 บาทอีกต่อไป</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>✅ เดิมเป็น known issue เปิดอยู่ (Lot-mode COGS ขึ้น 0 บาทเสมอ, v1/v2) — ตอนนี้ปิดแล้วจริง เป็นผลพลอยได้จากการแก้บั๊ก material_lot_id ในเคส TC-E2E-M2-05 (สาเหตุเดียวกัน: lot ที่ผูกผิดทำให้ FIFO หาต้นทุนที่ถูกต้องไม่เจอ) ยืนยันด้วยการรันจริงรอบนี้ COGS ขึ้นถูกต้องไม่ใช่ 0 อีกต่อไป</t>
+          <t>✅ เดิมเป็น known issue เปิดอยู่ (Lot-mode COGS ขึ้น 0 บาทเสมอ, v1/v2) — ปิดแล้วจริง ยืนยันซ้ำอีกครั้งด้วยการรันจริงรอบนี้ (2026-09-16) COGS ขึ้นถูกต้องไม่ใช่ 0</t>
         </is>
       </c>
       <c r="I8" s="7" t="n"/>

--- a/client-docs/test-cases/emg-o-test-cases-e2e-mode2.xlsx
+++ b/client-docs/test-cases/emg-o-test-cases-e2e-mode2.xlsx
@@ -12,6 +12,7 @@
     <sheet name="E2" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="E3" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="E4" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="E5" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C2:D12"/>
+  <dimension ref="C2:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="2" max="2"/>
@@ -484,14 +485,14 @@
     <row r="5">
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Total test cases: 13</t>
+          <t>Total test cases: 24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>High / Medium / Low: 9 / 4 / 0</t>
+          <t>High / Medium / Low: 16 / 8 / 0</t>
         </is>
       </c>
     </row>
@@ -545,6 +546,16 @@
       </c>
       <c r="D12" s="3" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>E5 — ตัดใหม่ (Cut Order — สร้าง Slab ใหม่จาก Block เมื่อยังไม่มีสต็อก)</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1529,4 +1540,596 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>E5. ตัดใหม่ (Cut Order — สร้าง Slab ใหม่จาก Block เมื่อยังไม่มีสต็อก) — ADR-061/066 — Factory สร้าง Manufacturing Order ตัด Block เองโดยตรงในแอป Manufacturing ไม่มี wizard อัตโนมัติจากบรรทัด SO แล้ว</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>TC ID</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>ข้อมูลตัวอย่าง (Sample Data)</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>Status (Pass/Fail)</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>TC-E2E-M2-13</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>เพิ่มบรรทัดสินค้าใน SO ทั้งที่ยังไม่มีแผ่นพร้อมขาย</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>ยังไม่มีแผ่นหินสถานะ Available ของ Material นี้เลย มีแต่ Block พร้อมอยู่ในสต็อก (ผ่านการซื้อ PO แบบเดียวกับ Mode 1)</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>1. เปิด Sales &gt; Orders &gt; New
+2. เลือกลูกค้า
+3. เพิ่มบรรทัด เลือกสินค้าของ Material นี้</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>ลูกค้า = "ทดสอบ E2E - Test Customer"
+สินค้า = E2E Mode2 Serial Fresh - Slab</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>เพิ่มบรรทัดสำเร็จ ปุ่ม "Select Slabs" ปรากฏเหมือนปกติ แต่ตอนนี้ยังไม่มีแผ่นให้เลือกเลย (0 Available) — ราคาที่ขึ้นเป็นแค่ List Price เริ่มต้น ต้องให้ Factory ตัดสต็อกใหม่ก่อนถึงจะขายได้จริง</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
+      <c r="J4" s="7" t="n"/>
+      <c r="K4" s="7" t="n"/>
+      <c r="L4" s="7" t="n"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>TC-E2E-M2-14</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Factory สร้าง Manufacturing Order ตัด Block ใหม่ (ขั้นตอนที่ 1-3)</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>ทำ TC-E2E-M2-13 เสร็จแล้ว (มี SO บรรทัดรออยู่), มี Block พร้อมอยู่ในสต็อก</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>1. เปิด Manufacturing &gt; New
+2. ช่อง "Stone Block" (ขั้นตอนที่ 1) เลือก Block ที่จะตัด — ระบบดึงสินค้า/BOM ที่จะผลิตให้อัตโนมัติ
+3. ช่อง "Target Slab L/H (M)" (ขั้นตอนที่ 2) ใส่ขนาดแผ่นที่ต้องการ — ระบบคำนวณจำนวนแผ่นที่จะได้ให้อัตโนมัติ (ดูที่แท็บ Planned/Actual Slabs)
+4. ช่อง "For Sale Order Line" (ขั้นตอนที่ 3) เลือกบรรทัด SO ที่รออยู่ แล้ว Save</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Stone Block = BLK-26-0037
+Target Slab L (M) = 1.20, Target Slab H (M) = 0.80
+For Sale Order Line = S00146</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>ระบบคำนวณจำนวนแผ่นที่จะผลิตอัตโนมัติจาก CBM ที่เหลือของ Block หารด้วยขนาดแผ่นที่ตั้ง (ตัวอย่างจริง: Block เหลือ 0.10 m³ ÷ (1.20×0.80×0.02) = 5 แผ่นพอดี) พร้อมสร้างบรรทัด Planned Slabs ให้ครบอัตโนมัติ — ถ้าต้องการตัดน้อยกว่าที่ระบบคำนวณ ลบบรรทัดส่วนเกินออกได้เองก่อน Confirm</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>✨ ฟีเจอร์ใหม่ session นี้ — Manufacturing Order เดิมไม่มีทางผูกกลับมาที่ SO ให้เห็นได้เลย (ปุ่ม MO มาตรฐานของ Odoo นับไม่ได้เพราะ Cut Order นี้ไม่ได้ผ่านกลไก Procurement) จึงเพิ่มปุ่ม "Cut Orders" ใหม่ไว้บน SO (ดู TC-E2E-M2-18)</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="n"/>
+      <c r="J5" s="7" t="n"/>
+      <c r="K5" s="7" t="n"/>
+      <c r="L5" s="7" t="n"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>TC-E2E-M2-15</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>ย้าย Block เข้าสถานีตัด (Move to Production) แล้ว Confirm MO</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>ทำ TC-E2E-M2-14 เสร็จแล้ว — ระบบเตือนว่า Block ยังไม่ได้อยู่ที่สถานีตัด (Stone Production) เพียงพอ</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>1. กดปุ่ม "ย้ายด่วน (Move to Production)" มุมบนซ้าย — ระบบสร้าง+ยืนยัน Internal Transfer ย้าย Block ไปสถานีตัดให้อัตโนมัติในคลิกเดียว
+2. กด "Confirm"</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>แถบเตือนสีเหลืองเปลี่ยนเป็นข้อความสีเขียว "พร้อม Confirm แล้ว" หลังย้ายสำเร็จ — กด Confirm ผ่านทันที ไม่ต้องออกไปทำ Internal Transfer เองใน Inventory</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
+      <c r="J6" s="7" t="n"/>
+      <c r="K6" s="7" t="n"/>
+      <c r="L6" s="7" t="n"/>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>TC-E2E-M2-16</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>ตัดจริงในแท็บ Work Orders แล้วกด Complete Cut</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>ทำ TC-E2E-M2-15 เสร็จแล้ว (MO สถานะ Confirmed)</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>1. ไปแท็บ "Work Orders" ดูขั้นตอนที่ต้องทำ (เช่น Transport, Gangsaw)
+2. ไปแท็บ "Planned/Actual Slabs" กรอกขนาดจริงที่ตัดได้ในคอลัมน์ Actual L/H/Thickness (ค่าเริ่มต้น = ตามแผน)
+3. กดปุ่ม "Complete Cut"</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>MO เปลี่ยนสถานะเป็น Done ทันที — ระบบสร้าง Slab ใหม่ครบตามแผนพร้อม Serial Number ให้อัตโนมัติในตัว (ตัวอย่างจริง: 5 แผ่น, Serial Numbers 5)</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="7" t="n"/>
+      <c r="J7" s="7" t="n"/>
+      <c r="K7" s="7" t="n"/>
+      <c r="L7" s="7" t="n"/>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>TC-E2E-M2-17</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>กลับไปที่ SO เดิม เลือกแผ่นที่เพิ่งตัดได้</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>ทำ TC-E2E-M2-16 เสร็จแล้ว</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>1. เปิด SO เดิมกลับมา (บรรทัดที่ทำไว้ใน TC-E2E-M2-13)
+2. กด "Select Slabs" บนบรรทัดนั้น</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>หน้าต่าง Select Slabs เตรียมแผ่นที่เพิ่งตัดได้มาให้อัตโนมัติแล้ว (สถานะ Hold ผูกกับบรรทัดนี้โดยตรง เพราะ MO ระบุ "For Sale Order Line" ไว้ตั้งแต่ต้น) ไม่ต้องกด Add a line เลือกเองซ้ำ — กด "Confirm Selection" ได้ทันที</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="7" t="n"/>
+      <c r="K8" s="7" t="n"/>
+      <c r="L8" s="7" t="n"/>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>TC-E2E-M2-18</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>ยืนยัน (Confirm) Sale Order — เช็คปุ่ม Cut Orders ปรากฏ</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>ทำ TC-E2E-M2-17 เสร็จแล้ว</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>1. กดปุ่ม Confirm บน Sale Order</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>SO เปลี่ยนสถานะเป็น Sales Order มี Delivery Order เกิดขึ้นอัตโนมัติ 1 ใบ — smart button ใหม่ "Cut Orders" ปรากฏที่มุมบน (นับ Manufacturing Order ที่ตัดมาเพื่อ SO นี้โดยเฉพาะ แยกจาก "Slabs") กดเข้าไปเปิด MO ที่ตัดให้ตรงตัวได้เลย — ตัวอย่างจริง: S00146 → EG01/OUT/00093, Total 4,622.40</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="7" t="n"/>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>TC-E2E-M2-19</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>พยายาม Validate ใบส่งของโดยยังไม่สแกน Serial ให้ตรง</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>ทำ TC-E2E-M2-18 เสร็จแล้ว มีใบส่งของสถานะ Ready รออยู่</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>1. เปิดใบส่งของ (Delivery) ที่เกิดขึ้นอัตโนมัติ
+2. กดปุ่ม Validate ทันทีโดยยังไม่กรอกช่อง "Scanned Serial" ให้ตรงกับ Serial ที่จองไว้</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>ระบบฟ้อง error สองภาษาทันทีเหมือน Mode 2 ปกติ: "สแกน Serial ไม่ตรง กรุณาสแกนให้ครบก่อน Validate" พร้อมระบุชื่อแผ่นที่ยังไม่ตรง (ตัวอย่างจริง: BLK-26-0037-1) บันทึกไม่ผ่าน</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>หมายเหตุ: กันส่งแผ่นผิดให้ลูกค้าโดยไม่ได้ตรวจสอบก่อน (ADR-009) — ใช้ตรรกะเดียวกับ Mode 2 ปกติ (TC-E2E-M2-07) ไม่ว่าแผ่นนั้นจะมาจากสต็อกเดิมหรือตัดใหม่</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="7" t="n"/>
+      <c r="K10" s="7" t="n"/>
+      <c r="L10" s="7" t="n"/>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>TC-E2E-M2-20</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>กรอก/สแกน Scanned Serial ให้ตรงแล้ว Validate</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>ทำ TC-E2E-M2-19 เสร็จแล้ว (เจอ error มาก่อน)</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>1. กด "Details" ที่บรรทัดสินค้า
+2. กรอกช่อง "Scanned Serial" ให้ตรงกับ Serial ที่จองไว้จริง แล้วกด Save
+3. กดปุ่ม Validate อีกครั้ง</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Scanned Serial = BLK-26-0037-1</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>ใบส่งของเปลี่ยนสถานะเป็น Done สำเร็จ — แผ่นที่ขายหายจากสต็อกที่ขายได้ (Available) แล้ว</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="7" t="n"/>
+      <c r="J11" s="7" t="n"/>
+      <c r="K11" s="7" t="n"/>
+      <c r="L11" s="7" t="n"/>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>TC-E2E-M2-21</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>สร้างและยืนยันใบแจ้งหนี้ — เช็คบัญชีรายได้ที่ใช้</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>ทำ TC-E2E-M2-20 เสร็จแล้ว</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>1. เปิด Sale Order &gt; กด "Create Invoice"
+2. เลือก "Regular invoice" &gt; Create Draft
+3. เปิดใบแจ้งหนี้ &gt; กด Confirm</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>ใบแจ้งหนี้สถานะ Posted ยอดรวมตรงกับ SO รวม VAT — ตัวอย่างจริง INV/2026/00039 (4,622.40) แต่บัญชีรายได้ที่ขึ้นคือ "Sales Revenue - Cut-to-Order (Mode 3)" ไม่ใช่ "Serial Slab Sale (Mode 2)" เหมือนบรรทัดที่ขายจากสต็อกที่มีอยู่แล้ว (ดูหมายเหตุ)</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>ℹ️ พฤติกรรมที่ตั้งใจไว้ ไม่ใช่บั๊ก — ระบบแยกบัญชีรายได้ตามว่า "แผ่นนี้ถูกตัดมาเพื่อออเดอร์นี้โดยเฉพาะ" (บัญชีนี้) หรือ "หยิบจากสต็อกที่ตัดไว้ก่อนแล้ว" (บัญชี Serial Slab Sale ปกติ ดู TC-E2E-M2-11) — ชื่อบัญชียังใช้คำว่า "Mode 3" หลงเหลือจากก่อนรวม Mode เข้ากับจุดขาย 2 ไม่กระทบความถูกต้องทางบัญชี เป็นแค่ชื่อที่อาจทำให้สับสนถ้าไม่รู้ที่มา — ควรพิจารณาเปลี่ยนชื่อบัญชีให้สื่อสารตรงกับจุดขาย 2 ในรอบถัดไป</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="n"/>
+      <c r="J12" s="7" t="n"/>
+      <c r="K12" s="7" t="n"/>
+      <c r="L12" s="7" t="n"/>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>TC-E2E-M2-22</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>ตรวจรายการบัญชี COGS/Inventory บนใบแจ้งหนี้</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>ทำ TC-E2E-M2-21 เสร็จแล้ว</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>1. เปิด Customer Invoice &gt; กด smart button "Journal Items"</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>เห็นคู่ COGS/Inventory แนบอัตโนมัติเหมือน Mode 2 ปกติ พร้อม Analytic Distribution ครบ — ตัวอย่างจริง INV/2026/00039: เดบิต "511110 COGS - Stone Sales (all modes)" / เครดิต "113110 Inventory - Stone Blocks (Raw)" คู่ละ 300.00 ยอดรวมสมดุล 4,922.40 = 4,922.40</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="7" t="n"/>
+      <c r="J13" s="7" t="n"/>
+      <c r="K13" s="7" t="n"/>
+      <c r="L13" s="7" t="n"/>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>TC-E2E-M2-23</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>รับชำระเงิน (Register Payment)</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>ทำ TC-E2E-M2-21 เสร็จแล้ว (Invoice = Posted)</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>1. เปิดใบแจ้งหนี้ &gt; กด "Pay"
+2. ตรวจ/ยืนยันยอดและวิธีชำระ &gt; กด Create Payment</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>ใบแจ้งหนี้ขึ้นสถานะ "In Payment" — จบเส้นทาง "ตัดใหม่" ทั้งหมดตั้งแต่ยังไม่มีสต็อกจนถึงรับเงินสำเร็จ (ตัวอย่างจริง: INV/2026/00039)</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="7" t="n"/>
+      <c r="K14" s="7" t="n"/>
+      <c r="L14" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>